--- a/skills/topic-dedup-check/out/选题去重清单.xlsx
+++ b/skills/topic-dedup-check/out/选题去重清单.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,8 +30,11 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <color rgb="009C0006"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +44,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002F5597"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -56,11 +64,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,11 +435,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -484,29 +493,181 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>测试选题A</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>面试被问期望薪资怎么答：3 个话术模板</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>热榜候选</t>
+        </is>
+      </c>
       <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>面试被问期望薪资怎么答：3 个话术模板</t>
+        </is>
+      </c>
       <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>🟢 通过</t>
+        <v>35</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>🔴 重复</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>库内无近似题</t>
+          <t>与《面试被问期望薪资怎么答：3 个话术模板》高度重合（35 天前）；差异化方向：换人群、换场景、换步骤数</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>被裁员那天我在工位坐到凌晨：3 个动作保住赔偿金</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>竞品爆款</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>裁员赔偿金谈判：N+1 怎么算</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>🟢 通过</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>库内最接近的题重合度低</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>领导让你口头汇报时，先说结论再说理由</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>评论区提问</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>汇报工作先说结论：金字塔原理的 3 步用法</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>120</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>🟢 通过</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>库内最接近的题重合度低</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>面试必问的 5 个问题及回答模板</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>搜索下拉词</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>面试被问期望薪资怎么答：3 个话术模板</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>35</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>🟢 通过</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>库内最接近的题重合度低</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>国庆假期后第一天上班，怎么快速找回状态</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>节点日历</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>裁员赔偿金谈判：N+1 怎么算</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>🟢 通过</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>库内最接近的题重合度低</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -547,7 +708,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -559,7 +720,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -571,7 +732,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -595,7 +756,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
